--- a/X-Lookup Function-1.xlsx
+++ b/X-Lookup Function-1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD5BE8EE-5616-4930-AC2E-7FD10807B224}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42167FC4-B9A2-42B7-A755-7272262F4662}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="53">
   <si>
     <t>Item ID</t>
   </si>
@@ -382,6 +382,12 @@
   </si>
   <si>
     <t>XLOOKUP</t>
+  </si>
+  <si>
+    <t>Item Id</t>
+  </si>
+  <si>
+    <t>Exact Match or Larger Item</t>
   </si>
 </sst>
 </file>
@@ -659,7 +665,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment readingOrder="1"/>
@@ -792,6 +798,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1648,7 +1655,7 @@
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="3" max="3" width="11" customWidth="1"/>
     <col min="4" max="4" width="11.77734375" customWidth="1"/>
-    <col min="6" max="6" width="4" customWidth="1"/>
+    <col min="6" max="6" width="13.33203125" customWidth="1"/>
     <col min="7" max="7" width="11.77734375" customWidth="1"/>
     <col min="8" max="10" width="15.5546875" customWidth="1"/>
   </cols>
@@ -1738,6 +1745,9 @@
       <c r="E6" s="2">
         <v>23</v>
       </c>
+      <c r="G6" s="16" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="7" spans="2:10">
       <c r="B7" s="5">
@@ -1766,6 +1776,18 @@
       <c r="E8" s="2">
         <v>32</v>
       </c>
+      <c r="G8" s="52" t="s">
+        <v>51</v>
+      </c>
+      <c r="H8" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="I8" s="52" t="s">
+        <v>2</v>
+      </c>
+      <c r="J8" s="52" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="9" spans="2:10">
       <c r="B9" s="5">
@@ -1778,6 +1800,19 @@
         <v>43983</v>
       </c>
       <c r="E9" s="2">
+        <v>32</v>
+      </c>
+      <c r="G9" s="9">
+        <v>109</v>
+      </c>
+      <c r="H9" s="9" t="str" cm="1">
+        <f t="array" ref="H9:J9">_xlfn.XLOOKUP(G9,$B$4:$B$10,$C$4:$E$10,"Data Not Found",1)</f>
+        <v>Keyboard</v>
+      </c>
+      <c r="I9" s="9">
+        <v>43862</v>
+      </c>
+      <c r="J9" s="9">
         <v>32</v>
       </c>
     </row>
@@ -1860,7 +1895,7 @@
         <v>45299</v>
       </c>
       <c r="H4" s="36">
-        <f>_xlfn.XLOOKUP(G4,$D$4:$D$10,$E$4:$E$10,"Data Not  Found",0)</f>
+        <f>_xlfn.XLOOKUP(G4,$D$4:$D$10,$E$4:$E$10,"Data Not  Found",0,2)</f>
         <v>32</v>
       </c>
     </row>
@@ -2327,11 +2362,11 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5655E9A4-9B56-4A6E-AEE0-3A1B3E47D4C9}">
-  <dimension ref="B1:H8"/>
+  <dimension ref="B1:H9"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="2.44140625" customWidth="1"/>
-    <col min="5" max="5" width="2.44140625" customWidth="1"/>
+    <col min="5" max="5" width="15.6640625" customWidth="1"/>
     <col min="6" max="8" width="12.109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2424,13 +2459,34 @@
       <c r="D8" s="20">
         <v>35000</v>
       </c>
+      <c r="F8" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="G8" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="H8" s="21" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8">
+      <c r="F9" s="42">
+        <v>100</v>
+      </c>
+      <c r="G9" s="41" t="s">
+        <v>23</v>
+      </c>
+      <c r="H9" cm="1">
+        <f t="array" ref="H9">_xlfn.XLOOKUP(F9&amp;G9,B4:B8&amp;C4:C8,D4:D8,"Data Not Found",0)</f>
+        <v>23000</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{91C59477-8B9B-474D-A3B3-8C12505B3D9C}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4 F9" xr:uid="{91C59477-8B9B-474D-A3B3-8C12505B3D9C}">
       <formula1>$B$4:$B$8</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G4" xr:uid="{281D2C3D-9C73-43C3-83BB-47F7D8BE79E0}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G4 G9" xr:uid="{281D2C3D-9C73-43C3-83BB-47F7D8BE79E0}">
       <formula1>$C$4:$C$8</formula1>
     </dataValidation>
   </dataValidations>
